--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="558">
   <si>
     <t>DFT</t>
   </si>
@@ -649,9 +649,6 @@
   </si>
   <si>
     <t>Green chemistry</t>
-  </si>
-  <si>
-    <t>Note: Table 20/Fig. 12 baseline (0.25/0.35/0.40) differs from the weights in Tables 10/13 and Fig. 5B (0.30/0.30/0.40). Both sum to 1. After each ±10% change the other weights are renormalised to sum to 1.</t>
   </si>
   <si>
     <t>Outcome (Table 20)</t>
@@ -2511,21 +2508,21 @@
         <v>103</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B4" s="18">
         <f>COUNTA(Pathways_48!A12:A59)</f>
@@ -2540,12 +2537,12 @@
         <v>OK</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B5" s="18">
         <f>SUM(Pathways_48!D12:D59)</f>
@@ -2560,12 +2557,12 @@
         <v>OK</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B6" s="18">
         <f>SUM(Pathways_48!I12:I59)</f>
@@ -2580,12 +2577,12 @@
         <v>OK</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B7" s="18">
         <f>SUM(Pathways_48!M12:M59)</f>
@@ -2600,12 +2597,12 @@
         <v>OK</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B8" s="18">
         <f>SUM(Pathways_48!S12:S59)</f>
@@ -2620,12 +2617,12 @@
         <v>OK</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B9" s="18">
         <f>SUM(Pathways_48!T12:T59)</f>
@@ -2640,12 +2637,12 @@
         <v>OK</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B10" s="18">
         <f>AVERAGE(Pathways_48!C12:C59)</f>
@@ -2665,7 +2662,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B11" s="18">
         <f>MEDIAN(Pathways_48!C12:C59)</f>
@@ -2685,7 +2682,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B12" s="18">
         <f>STDEV(Pathways_48!C12:C59)</f>
@@ -2705,7 +2702,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B13" s="18">
         <f>MIN(Pathways_48!C12:C59)</f>
@@ -2725,7 +2722,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B14" s="18">
         <f>MAX(Pathways_48!C12:C59)</f>
@@ -2745,7 +2742,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B15" s="18">
         <f>COUNTIF(Pathways_48!C12:C59,"&gt;0.8")</f>
@@ -2765,7 +2762,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B16" s="18">
         <f>AVERAGE(Pathways_48!C12:C42)</f>
@@ -2780,12 +2777,12 @@
         <v>OK</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B17" s="18">
         <f>MEDIAN(Pathways_48!C12:C42)</f>
@@ -2805,7 +2802,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B18" s="18">
         <f>STDEV(Pathways_48!C12:C42)</f>
@@ -2820,12 +2817,12 @@
         <v>OK</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B19" s="18">
         <f>MIN(Pathways_48!C12:C42)</f>
@@ -2840,12 +2837,12 @@
         <v>OK</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B20" s="18">
         <f>MAX(Pathways_48!C12:C42)</f>
@@ -2860,12 +2857,12 @@
         <v>OK</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B21" s="18">
         <f>COUNTIF(Pathways_48!C12:C42,"&gt;0.8")</f>
@@ -2885,7 +2882,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B22" s="18">
         <f>MIN(Pathways_48!E12:E29)</f>
@@ -2900,12 +2897,12 @@
         <v>OK</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B23" s="18">
         <f>MAX(Pathways_48!E12:E29)</f>
@@ -2920,12 +2917,12 @@
         <v>OK</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B24" s="18">
         <f>MIN(Pathways_48!F12:F29)</f>
@@ -2940,12 +2937,12 @@
         <v>OK</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B25" s="18">
         <f>MAX(Pathways_48!F12:F29)</f>
@@ -2960,12 +2957,12 @@
         <v>OK</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B26" s="18">
         <f>RSQ(Pathways_48!E12:E29,Pathways_48!F12:F29)</f>
@@ -2980,12 +2977,12 @@
         <v>OK</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B27" s="18">
         <f>ABS(CORREL(Pathways_48!F12:F29,Pathways_48!E12:E29))</f>
@@ -3000,12 +2997,12 @@
         <v>OK</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B28" s="18" t="str">
         <f>IF(MAX(Pathways_48!H12:H29)&lt;0,"Yes","No")</f>
@@ -3019,12 +3016,12 @@
         <v>OK</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B29" s="18">
         <f>MAX(Pathways_48!G12:G29)</f>
@@ -3039,12 +3036,12 @@
         <v>OK</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B30" s="18">
         <f>MAX(Pathways_48!J12:J20)</f>
@@ -3059,12 +3056,12 @@
         <v>OK</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B31" s="18">
         <f>MIN(Pathways_48!J12:J20)</f>
@@ -3079,12 +3076,12 @@
         <v>OK</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B32" s="18">
         <f>MIN(Pathways_48!K12:K20)</f>
@@ -3099,12 +3096,12 @@
         <v>OK</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B33" s="18">
         <f>MAX(Pathways_48!K12:K20)</f>
@@ -3119,12 +3116,12 @@
         <v>OK</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B34" s="18">
         <f>MIN(Pathways_48!L12:L20)</f>
@@ -3139,12 +3136,12 @@
         <v>OK</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B35" s="18">
         <f>MAX(Pathways_48!L12:L20)</f>
@@ -3159,12 +3156,12 @@
         <v>OK</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B36" s="18">
         <f>MIN(Pathways_48!Q12:Q20)</f>
@@ -3179,12 +3176,12 @@
         <v>OK</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B37" s="18">
         <f>MAX(Pathways_48!Q12:Q20)</f>
@@ -3199,12 +3196,12 @@
         <v>OK</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B38" s="18" t="str">
         <f>IF(Pathways_48!T14=1,"Yes","No")</f>
@@ -3218,12 +3215,12 @@
         <v>OK</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B39" s="18" t="str">
         <f>IF(AND(Pathways_48!S14=1,Pathways_48!S15=1,Pathways_48!S13=1,SUM(Pathways_48!S12:S59)=3),"Yes","No")</f>
@@ -3237,12 +3234,12 @@
         <v>OK</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D41" s="9" t="str">
         <f>IF(COUNTIF(D4:D39,"OK")=ROWS(D4:D39),"ALL MATCH","CHECK")</f>
@@ -3273,231 +3270,231 @@
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>396</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>398</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>400</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>402</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>404</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>406</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>408</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>410</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>412</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>414</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>416</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="D18" s="6" t="s">
         <v>425</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="6" t="s">
         <v>429</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>431</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>433</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>441</v>
-      </c>
       <c r="D22" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>444</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>446</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>448</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3505,13 +3502,13 @@
         <v>36</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3519,13 +3516,13 @@
         <v>165</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>459</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3533,107 +3530,107 @@
         <v>125</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="D30" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>466</v>
-      </c>
       <c r="D31" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>469</v>
-      </c>
       <c r="D32" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="23" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>472</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>480</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>482</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="23" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3641,10 +3638,10 @@
         <v>3</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3652,10 +3649,10 @@
         <v>202</v>
       </c>
       <c r="B45" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>486</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3663,10 +3660,10 @@
         <v>0</v>
       </c>
       <c r="B46" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>488</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3674,70 +3671,70 @@
         <v>1</v>
       </c>
       <c r="B47" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>490</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="C48" s="6" t="s">
         <v>493</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="23" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="C51" s="4" t="s">
         <v>496</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>498</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="C53" s="6" t="s">
         <v>501</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>504</v>
-      </c>
       <c r="C54" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3745,10 +3742,10 @@
         <v>165</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3759,7 +3756,7 @@
         <v>124</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3767,80 +3764,80 @@
         <v>125</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="23" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="C60" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="C61" s="6" t="s">
         <v>512</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C62" s="6" t="s">
         <v>514</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B63" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>512</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="C64" s="6" t="s">
         <v>518</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>202</v>
@@ -3849,109 +3846,109 @@
         <v>0</v>
       </c>
       <c r="D67" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="E67" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="F67" s="4" t="s">
         <v>523</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="C68" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="C68" s="6" t="s">
-        <v>527</v>
-      </c>
       <c r="D68" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B69" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="D69" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="E69" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>527</v>
-      </c>
       <c r="F69" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B70" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="C70" s="6" t="s">
-        <v>527</v>
-      </c>
       <c r="D70" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>527</v>
-      </c>
       <c r="F70" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="23" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>2</v>
@@ -3959,72 +3956,72 @@
     </row>
     <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="C75" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="D75" s="6" t="s">
         <v>534</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="C77" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D77" s="6" t="s">
         <v>538</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>463</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4035,10 +4032,10 @@
         <v>165</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4049,10 +4046,10 @@
         <v>124</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4063,79 +4060,79 @@
         <v>125</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>542</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>544</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>546</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>548</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="B89" s="6" t="s">
         <v>550</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>552</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>554</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B92" s="6" t="s">
         <v>556</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -5585,7 +5582,7 @@
         <v>1.2999999999999901E-2</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="K16" s="27">
         <f>(C16-$B$4*D16-$B$5*E16)/$B$6</f>
@@ -5964,9 +5961,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
-        <v>205</v>
-      </c>
+      <c r="A8" s="32"/>
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
@@ -5977,22 +5972,22 @@
     </row>
     <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>211</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>29</v>
@@ -6000,7 +5995,7 @@
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B11" s="12">
         <v>0.96</v>
@@ -6012,12 +6007,12 @@
         <v>0.98</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B12" s="19">
         <v>0.94</v>
@@ -6037,12 +6032,12 @@
         <v>0.95799999999999996</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B13" s="19">
         <v>1.7999999999999999E-2</v>
@@ -6050,7 +6045,7 @@
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B14" s="19">
         <v>1.4999999999999999E-2</v>
@@ -6058,7 +6053,7 @@
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B15" s="5">
         <v>20</v>
@@ -6066,15 +6061,15 @@
     </row>
     <row r="17" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>219</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" s="8">
         <v>0.58299999999999996</v>
@@ -6082,7 +6077,7 @@
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B19" s="8">
         <v>0.247</v>
@@ -6090,7 +6085,7 @@
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B20" s="7">
         <f>B18+B19</f>
@@ -6099,21 +6094,21 @@
     </row>
     <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B23" s="28">
         <v>0.94099999999999995</v>
@@ -6127,7 +6122,7 @@
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B24" s="28">
         <v>0.93600000000000005</v>
@@ -6141,7 +6136,7 @@
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B25" s="28">
         <v>0.93200000000000005</v>
@@ -6155,22 +6150,22 @@
     </row>
     <row r="28" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="C28" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6275,7 +6270,7 @@
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B34" s="6" t="str">
         <f>IF(AND(B29&gt;MAX(B30:B33),C29&gt;MAX(C30:C33),D29&gt;MAX(D30:D33),E29&gt;MAX(E30:E33),F29&gt;MAX(F30:F33)),"Yes","No")</f>
@@ -6505,16 +6500,16 @@
     </row>
     <row r="3" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>90</v>
@@ -6529,15 +6524,15 @@
         <v>125</v>
       </c>
       <c r="I3" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B4" s="5">
         <v>48</v>
@@ -6571,7 +6566,7 @@
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B5" s="5">
         <v>45</v>
@@ -6605,7 +6600,7 @@
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B6" s="5">
         <v>41</v>
@@ -6639,7 +6634,7 @@
     </row>
     <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B8" s="6" t="str">
         <f>IF(AND(D4=Composite!C16,E4=DFT!B7,F4=Green!B6,G4=Green!C6,H4=Green!D6),"OK","CHECK")</f>
@@ -6648,56 +6643,56 @@
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B12" s="10">
         <v>0.92</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B13" s="10">
         <v>0.63</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>119</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="32" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B16" s="32"/>
       <c r="C16" s="32"/>
@@ -6769,76 +6764,76 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B4" s="29">
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B5" s="29">
         <v>5.65</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B6" s="29">
         <v>58</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B7" s="29">
         <v>40</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="51" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B8" s="29">
         <v>32</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>90</v>
@@ -6847,13 +6842,13 @@
         <v>91</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>93</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>123</v>
@@ -6865,36 +6860,36 @@
         <v>125</v>
       </c>
       <c r="M11" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="N11" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="O11" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="O11" s="4" t="s">
+      <c r="P11" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="P11" s="4" t="s">
+      <c r="Q11" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="Q11" s="4" t="s">
+      <c r="R11" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="S11" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="S11" s="4" t="s">
+      <c r="T11" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="T11" s="4" t="s">
+      <c r="U11" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="U11" s="4" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>95</v>
@@ -6976,7 +6971,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>97</v>
@@ -7058,7 +7053,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>99</v>
@@ -7140,7 +7135,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>101</v>
@@ -7222,7 +7217,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>102</v>
@@ -7304,10 +7299,10 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>289</v>
       </c>
       <c r="C17" s="24">
         <v>0.76</v>
@@ -7376,10 +7371,10 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>290</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>291</v>
       </c>
       <c r="C18" s="24">
         <v>0.86</v>
@@ -7448,10 +7443,10 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="C19" s="24">
         <v>0.71</v>
@@ -7520,10 +7515,10 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>295</v>
       </c>
       <c r="C20" s="24">
         <v>0.85</v>
@@ -7592,7 +7587,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>13</v>
@@ -7655,7 +7650,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>13</v>
@@ -7718,7 +7713,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>13</v>
@@ -7781,7 +7776,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>13</v>
@@ -7844,7 +7839,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>13</v>
@@ -7907,7 +7902,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>13</v>
@@ -7970,7 +7965,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>13</v>
@@ -8033,7 +8028,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>13</v>
@@ -8096,7 +8091,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>13</v>
@@ -8159,7 +8154,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>13</v>
@@ -8216,7 +8211,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>13</v>
@@ -8273,7 +8268,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>13</v>
@@ -8330,7 +8325,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>13</v>
@@ -8387,7 +8382,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>13</v>
@@ -8444,7 +8439,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>13</v>
@@ -8501,7 +8496,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>13</v>
@@ -8558,7 +8553,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>13</v>
@@ -8615,7 +8610,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>13</v>
@@ -8672,7 +8667,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>13</v>
@@ -8729,7 +8724,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>13</v>
@@ -8786,7 +8781,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>13</v>
@@ -8843,7 +8838,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>13</v>
@@ -8900,7 +8895,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>13</v>
@@ -8949,7 +8944,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>13</v>
@@ -8998,7 +8993,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>13</v>
@@ -9047,7 +9042,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>13</v>
@@ -9096,7 +9091,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>13</v>
@@ -9145,7 +9140,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>13</v>
@@ -9194,7 +9189,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>13</v>
@@ -9243,7 +9238,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>13</v>
@@ -9292,7 +9287,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>13</v>
@@ -9341,7 +9336,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>13</v>
@@ -9390,7 +9385,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>13</v>
@@ -9439,7 +9434,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>13</v>
@@ -9488,7 +9483,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>13</v>
@@ -9537,7 +9532,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>13</v>
@@ -9586,7 +9581,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>13</v>
@@ -9635,7 +9630,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>13</v>
@@ -9684,7 +9679,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>13</v>
@@ -9733,7 +9728,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="62" spans="1:21" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\Accept\green chem AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\AppData\Local\Temp\Rar$DIa8496.17801.rartemp\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" tabRatio="500" firstSheet="7" activeTab="10"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530" tabRatio="500" firstSheet="7" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Funnel" sheetId="2" r:id="rId1"/>
